--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -113,94 +113,22 @@
     <t/>
   </si>
   <si>
-    <t>Card.TbPlayerCard</t>
-  </si>
-  <si>
-    <t>PlayerCard</t>
-  </si>
-  <si>
-    <t>PlayerCard@Card.xlsx</t>
-  </si>
-  <si>
-    <t>Card.TbRecipe</t>
-  </si>
-  <si>
-    <t>Recipe</t>
-  </si>
-  <si>
-    <t>Recipe@Card.xlsx</t>
-  </si>
-  <si>
-    <t>Player.TbPlayerClassDeck</t>
-  </si>
-  <si>
-    <t>PlayerClassDeck</t>
-  </si>
-  <si>
-    <t>PlayerClassDeck@Card.xlsx</t>
-  </si>
-  <si>
-    <t>TbAsset</t>
-  </si>
-  <si>
-    <t>Asset</t>
-  </si>
-  <si>
-    <t>Asset@Card.xlsx</t>
-  </si>
-  <si>
-    <t>CardSkill.TbSkill</t>
-  </si>
-  <si>
-    <t>Skill</t>
-  </si>
-  <si>
-    <t>Skill@Card.xlsx,BespokeSkill@Card.xlsx</t>
-  </si>
-  <si>
-    <t>Enemy.TbMvpEnemyCard</t>
-  </si>
-  <si>
-    <t>MvpEnemyCard</t>
-  </si>
-  <si>
-    <t>MvpEnemyCard@Card.xlsx</t>
-  </si>
-  <si>
-    <t>Enemy.TbMvpRewardPool</t>
-  </si>
-  <si>
-    <t>MvpRewardPool</t>
-  </si>
-  <si>
-    <t>MvpRewardPool@Card.xlsx</t>
-  </si>
-  <si>
-    <t>Config.TbPlayerConfig</t>
-  </si>
-  <si>
-    <t>PlayerConfig</t>
-  </si>
-  <si>
-    <t>PlayerConfig@Player.xlsx</t>
-  </si>
-  <si>
-    <t>Config.TbGameplayConfig</t>
-  </si>
-  <si>
-    <t>GameplayConfig</t>
-  </si>
-  <si>
-    <t>GameplayConfig@Player.xlsx</t>
-  </si>
-  <si>
-    <t>Enemy.TbUndercityCard</t>
-  </si>
-  <si>
-    <t>UndercityCard</t>
-  </si>
-  <si>
-    <t>UndercityCard@Card.xlsx</t>
+    <t>TbItem</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Item@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbDogSkin</t>
+  </si>
+  <si>
+    <t>DogSkin</t>
+  </si>
+  <si>
+    <t>DogSkin@Main.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1157,8 +1085,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.1111111111111" style="2" customWidth="1"/>
@@ -1313,157 +1241,6 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="B9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="B11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="B12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="B13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -129,6 +129,24 @@
   </si>
   <si>
     <t>DogSkin@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbPayTable</t>
+  </si>
+  <si>
+    <t>PayTable</t>
+  </si>
+  <si>
+    <t>PayTable@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbGameDevelopConfig</t>
+  </si>
+  <si>
+    <t>GameDevelopConfig</t>
+  </si>
+  <si>
+    <t>GameDevelopConfig@Main.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1085,8 +1103,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4" outlineLevelRow="4"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.1111111111111" style="2" customWidth="1"/>
@@ -1241,6 +1259,34 @@
         <v>33</v>
       </c>
     </row>
+    <row r="6" spans="1:11">
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -147,6 +147,15 @@
   </si>
   <si>
     <t>GameDevelopConfig@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbRarity</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Rarity@Main.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1103,8 +1112,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4" outlineLevelRow="6"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.1111111111111" style="2" customWidth="1"/>
@@ -1287,6 +1296,20 @@
         <v>39</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -149,13 +149,13 @@
     <t>GameDevelopConfig@Main.xlsx</t>
   </si>
   <si>
-    <t>TbRarity</t>
-  </si>
-  <si>
-    <t>Rarity</t>
-  </si>
-  <si>
-    <t>Rarity@Main.xlsx</t>
+    <t>TbRarityUI</t>
+  </si>
+  <si>
+    <t>RarityUI</t>
+  </si>
+  <si>
+    <t>RarityUI@Main.xlsx</t>
   </si>
 </sst>
 </file>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -156,6 +156,15 @@
   </si>
   <si>
     <t>RarityUI@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbTabGroup</t>
+  </si>
+  <si>
+    <t>TabGroup</t>
+  </si>
+  <si>
+    <t>TabGroup@Main.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1112,8 +1121,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.1111111111111" style="2" customWidth="1"/>
@@ -1310,6 +1319,20 @@
         <v>42</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -165,6 +165,15 @@
   </si>
   <si>
     <t>TabGroup@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbDogReaction</t>
+  </si>
+  <si>
+    <t>DogReaction</t>
+  </si>
+  <si>
+    <t>DogReaction@Main.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1130,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1333,6 +1342,20 @@
         <v>45</v>
       </c>
     </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -174,6 +174,15 @@
   </si>
   <si>
     <t>DogReaction@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbEquipmentSlotConfig</t>
+  </si>
+  <si>
+    <t>EquipmentSlotConfig</t>
+  </si>
+  <si>
+    <t>EquipmentSlotConfig@Main.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1130,12 +1139,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.1111111111111" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.6666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.6666666666667" style="2" customWidth="1"/>
     <col min="5" max="5" width="47.1111111111111" style="2" customWidth="1"/>
     <col min="6" max="6" width="114.222222222222" style="2" customWidth="1"/>
@@ -1356,6 +1365,20 @@
         <v>48</v>
       </c>
     </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -183,6 +183,15 @@
   </si>
   <si>
     <t>EquipmentSlotConfig@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbDesktopActivityState</t>
+  </si>
+  <si>
+    <t>DesktopActivityState</t>
+  </si>
+  <si>
+    <t>DesktopActivityState@Main.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1379,6 +1388,20 @@
         <v>51</v>
       </c>
     </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -110,7 +110,58 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t/>
+    <t>TbDogSkin</t>
+  </si>
+  <si>
+    <t>DogSkin</t>
+  </si>
+  <si>
+    <t>DogSkin@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbPayTable</t>
+  </si>
+  <si>
+    <t>PayTable</t>
+  </si>
+  <si>
+    <t>PayTable@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbGameDevelopConfig</t>
+  </si>
+  <si>
+    <t>GameDevelopConfig</t>
+  </si>
+  <si>
+    <t>GameDevelopConfig@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbRarityUI</t>
+  </si>
+  <si>
+    <t>RarityUI</t>
+  </si>
+  <si>
+    <t>RarityUI@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbDogReaction</t>
+  </si>
+  <si>
+    <t>DogReaction</t>
+  </si>
+  <si>
+    <t>DogReaction@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbDesktopActivityState</t>
+  </si>
+  <si>
+    <t>DesktopActivityState</t>
+  </si>
+  <si>
+    <t>DesktopActivityState@Main.xlsx</t>
   </si>
   <si>
     <t>TbItem</t>
@@ -119,43 +170,7 @@
     <t>Item</t>
   </si>
   <si>
-    <t>Item@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbDogSkin</t>
-  </si>
-  <si>
-    <t>DogSkin</t>
-  </si>
-  <si>
-    <t>DogSkin@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbPayTable</t>
-  </si>
-  <si>
-    <t>PayTable</t>
-  </si>
-  <si>
-    <t>PayTable@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbGameDevelopConfig</t>
-  </si>
-  <si>
-    <t>GameDevelopConfig</t>
-  </si>
-  <si>
-    <t>GameDevelopConfig@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbRarityUI</t>
-  </si>
-  <si>
-    <t>RarityUI</t>
-  </si>
-  <si>
-    <t>RarityUI@Main.xlsx</t>
+    <t>Item@Items.xlsx</t>
   </si>
   <si>
     <t>TbTabGroup</t>
@@ -164,16 +179,7 @@
     <t>TabGroup</t>
   </si>
   <si>
-    <t>TabGroup@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbDogReaction</t>
-  </si>
-  <si>
-    <t>DogReaction</t>
-  </si>
-  <si>
-    <t>DogReaction@Main.xlsx</t>
+    <t>TabGroup@Items.xlsx</t>
   </si>
   <si>
     <t>TbEquipmentSlotConfig</t>
@@ -182,16 +188,52 @@
     <t>EquipmentSlotConfig</t>
   </si>
   <si>
-    <t>EquipmentSlotConfig@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbDesktopActivityState</t>
-  </si>
-  <si>
-    <t>DesktopActivityState</t>
-  </si>
-  <si>
-    <t>DesktopActivityState@Main.xlsx</t>
+    <t>EquipmentSlotConfig@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbBlindBox</t>
+  </si>
+  <si>
+    <t>BlindBox</t>
+  </si>
+  <si>
+    <t>BlindBox@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbBlindBoxSchedule</t>
+  </si>
+  <si>
+    <t>BlindBoxSchedule</t>
+  </si>
+  <si>
+    <t>BlindBoxSchedule@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbBlindBoxRarityRate</t>
+  </si>
+  <si>
+    <t>BlindBoxRarityRate</t>
+  </si>
+  <si>
+    <t>BlindBoxRarityRate@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbBlindBoxRevealPath</t>
+  </si>
+  <si>
+    <t>BlindBoxRevealPath</t>
+  </si>
+  <si>
+    <t>BlindBoxRevealPath@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbBlindBoxVisual</t>
+  </si>
+  <si>
+    <t>BlindBoxVisual</t>
+  </si>
+  <si>
+    <t>BlindBoxVisual@Items.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1148,14 +1190,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.1111111111111" style="2" customWidth="1"/>
     <col min="3" max="3" width="26" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.6666666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="47.1111111111111" style="2" customWidth="1"/>
+    <col min="5" max="5" width="50.5555555555556" style="2" customWidth="1"/>
     <col min="6" max="6" width="114.222222222222" style="2" customWidth="1"/>
     <col min="7" max="7" width="40.4444444444444" style="2" customWidth="1"/>
     <col min="8" max="8" width="70" style="2" customWidth="1"/>
@@ -1256,150 +1298,204 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="B9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D9" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>48</v>
+      <c r="A10" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="2" t="s">
         <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -162,6 +162,15 @@
   </si>
   <si>
     <t>DesktopActivityState@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbBGMList</t>
+  </si>
+  <si>
+    <t>BGMList</t>
+  </si>
+  <si>
+    <t>BGMList@Main.xlsx</t>
   </si>
   <si>
     <t>TbItem</t>
@@ -1190,7 +1199,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1382,22 +1391,22 @@
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1496,6 +1505,20 @@
       </c>
       <c r="E18" s="2" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -171,6 +171,15 @@
   </si>
   <si>
     <t>BGMList@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbAchievement</t>
+  </si>
+  <si>
+    <t>Achievement</t>
+  </si>
+  <si>
+    <t>Achievement@Main.xlsx</t>
   </si>
   <si>
     <t>TbItem</t>
@@ -1199,7 +1208,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1405,22 +1414,22 @@
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="B12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1519,6 +1528,20 @@
       </c>
       <c r="E19" s="2" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -180,6 +180,15 @@
   </si>
   <si>
     <t>Achievement@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbPlayerStatistic</t>
+  </si>
+  <si>
+    <t>PlayerStatistic</t>
+  </si>
+  <si>
+    <t>PlayerStatistic@Main.xlsx</t>
   </si>
   <si>
     <t>TbItem</t>
@@ -1208,7 +1217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1428,22 +1437,22 @@
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="B13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1542,6 +1551,20 @@
       </c>
       <c r="E20" s="2" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
@@ -261,6 +261,15 @@
   </si>
   <si>
     <t>BlindBoxVisual@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbLinkTree</t>
+  </si>
+  <si>
+    <t>LinkTree</t>
+  </si>
+  <si>
+    <t>LinkTree@Items.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1226,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1567,6 +1576,20 @@
         <v>77</v>
       </c>
     </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
   <si>
     <t>##var</t>
   </si>
@@ -270,6 +270,15 @@
   </si>
   <si>
     <t>LinkTree@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbSteamItemDef</t>
+  </si>
+  <si>
+    <t>SteamItemDef</t>
+  </si>
+  <si>
+    <t>SteamItemDef@Items.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1590,6 +1599,20 @@
         <v>80</v>
       </c>
     </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -279,6 +279,15 @@
   </si>
   <si>
     <t>SteamItemDef@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbSteamItemDefIdRange</t>
+  </si>
+  <si>
+    <t>SteamItemDefIdRange</t>
+  </si>
+  <si>
+    <t>SteamItemDefIdRange@Items.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1613,6 +1622,20 @@
         <v>83</v>
       </c>
     </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
   <si>
     <t>##var</t>
   </si>
@@ -189,6 +189,15 @@
   </si>
   <si>
     <t>PlayerStatistic@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbInteractionHintConfig</t>
+  </si>
+  <si>
+    <t>InteractionHintConfig</t>
+  </si>
+  <si>
+    <t>InteractionHintConfig@Main.xlsx</t>
   </si>
   <si>
     <t>TbItem</t>
@@ -1244,7 +1253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1478,22 +1487,22 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="B14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1634,6 +1643,20 @@
       </c>
       <c r="E24" s="2" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
   <si>
     <t>##var</t>
   </si>
@@ -297,6 +297,15 @@
   </si>
   <si>
     <t>SteamItemDefIdRange@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbRefreshmentConfig</t>
+  </si>
+  <si>
+    <t>RefreshmentConfig</t>
+  </si>
+  <si>
+    <t>RefreshmentConfig@Items.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1253,7 +1262,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1659,6 +1668,20 @@
         <v>89</v>
       </c>
     </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/xlsx/__tables__.xlsx
+++ b/luban-excels/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>##var</t>
   </si>
@@ -306,12 +306,24 @@
   </si>
   <si>
     <t>RefreshmentConfig@Items.xlsx</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TbBlindBoxItemWeight</t>
+  </si>
+  <si>
+    <t>BlindBoxItemWeight</t>
+  </si>
+  <si>
+    <t>BlindBoxItemWeight@Items.xlsx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -320,166 +332,166 @@
   </numFmts>
   <fonts count="22">
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF006100"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF006100"/>
       <sz val="12"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
       <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -788,148 +800,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -937,10 +949,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -995,7 +1007,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1005,7 +1017,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1256,30 +1268,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
-    <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
-    <col min="2" max="2" width="32.1111111111111" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.6666666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="50.5555555555556" style="2" customWidth="1"/>
-    <col min="6" max="6" width="114.222222222222" style="2" customWidth="1"/>
-    <col min="7" max="7" width="40.4444444444444" style="2" customWidth="1"/>
-    <col min="8" max="8" width="70" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.11111111111111" style="2" customWidth="1"/>
-    <col min="11" max="11" width="43.8888888888889" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col customWidth="true" max="1" min="1" style="2" width="7.88888888888889"/>
+    <col customWidth="true" max="2" min="2" style="2" width="32.1111111111111"/>
+    <col customWidth="true" max="3" min="3" style="2" width="26"/>
+    <col customWidth="true" max="4" min="4" style="2" width="16.6666666666667"/>
+    <col customWidth="true" max="5" min="5" style="2" width="50.5555555555556"/>
+    <col customWidth="true" max="6" min="6" style="2" width="114.222222222222"/>
+    <col customWidth="true" max="7" min="7" style="2" width="40.4444444444444"/>
+    <col customWidth="true" max="8" min="8" style="2" width="70"/>
+    <col customWidth="true" max="9" min="9" style="2" width="12"/>
+    <col customWidth="true" max="10" min="10" style="2" width="6.11111111111111"/>
+    <col customWidth="true" max="11" min="11" style="2" width="43.8888888888889"/>
+    <col max="16384" min="12" style="2" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" spans="1:11" s="1" customFormat="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1314,7 +1327,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" spans="1:11" s="1" customFormat="true">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1346,7 +1359,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" spans="1:11" s="1" customFormat="true">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1682,9 +1695,44 @@
         <v>92</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <headerFooter/>
 </worksheet>
 </file>